--- a/OUTPUT/gate_oof/fold_2/expert_inner_metrics.xlsx
+++ b/OUTPUT/gate_oof/fold_2/expert_inner_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,10 +535,10 @@
         <v>460</v>
       </c>
       <c r="H2" t="n">
-        <v>2.645238700000846</v>
+        <v>2.79722580005182</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03378049999992072</v>
+        <v>0.02010510000400245</v>
       </c>
       <c r="J2" t="n">
         <v>0.003641065717330725</v>
@@ -587,31 +587,31 @@
         <v>752</v>
       </c>
       <c r="H3" t="n">
-        <v>6.916369799999302</v>
+        <v>4.039174799981993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5946097999985795</v>
+        <v>0.5277172999922186</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005482496793242469</v>
+        <v>0.005490185255488143</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00392919882556112</v>
+        <v>0.003933164688724057</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7205260974782368</v>
+        <v>0.7197416989541869</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4092871000199506</v>
+        <v>0.4097134025775159</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0001996111574219709</v>
+        <v>-0.0001819527006047117</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01147181631238815</v>
+        <v>0.01150642067800913</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02212169069622971</v>
+        <v>0.02219914701670012</v>
       </c>
     </row>
     <row r="4">
@@ -639,31 +639,31 @@
         <v>1442</v>
       </c>
       <c r="H4" t="n">
-        <v>12.89355310000064</v>
+        <v>7.634928699990269</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5198872000000847</v>
+        <v>0.4213255000067875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005338918519383596</v>
+        <v>0.005355972506205287</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004075047453622849</v>
+        <v>0.004086862921059451</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6008684043979589</v>
+        <v>0.5983144578162678</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4131568450580387</v>
+        <v>0.4143525972029836</v>
       </c>
       <c r="N4" t="n">
-        <v>1.014902286858788e-05</v>
+        <v>3.212143505496446e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01083947295436701</v>
+        <v>0.01103682046220762</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01986663465339278</v>
+        <v>0.01994379788597367</v>
       </c>
     </row>
     <row r="5">
@@ -691,10 +691,10 @@
         <v>460</v>
       </c>
       <c r="H5" t="n">
-        <v>2.910664099999849</v>
+        <v>2.088292500004172</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03454260000034992</v>
+        <v>0.02374620002228767</v>
       </c>
       <c r="J5" t="n">
         <v>0.003365214816730224</v>
@@ -743,31 +743,31 @@
         <v>752</v>
       </c>
       <c r="H6" t="n">
-        <v>6.612985300000219</v>
+        <v>3.935647999984212</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5235713000001851</v>
+        <v>0.406742800027132</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005607271550176241</v>
+        <v>0.005613694092364075</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004016026209405941</v>
+        <v>0.004020550516241834</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7085068506978007</v>
+        <v>0.707838718543041</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4185626549347581</v>
+        <v>0.4190234459308244</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.653362305034371e-05</v>
+        <v>-8.18829556224962e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01223890719356993</v>
+        <v>0.01245572847561072</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02127321158894968</v>
+        <v>0.0213670394590737</v>
       </c>
     </row>
     <row r="7">
@@ -795,31 +795,31 @@
         <v>1442</v>
       </c>
       <c r="H7" t="n">
-        <v>11.20860859999993</v>
+        <v>7.178740400006063</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5460896999993565</v>
+        <v>0.3970460999989882</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005530318501540773</v>
+        <v>0.005531572662191605</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004226405601610877</v>
+        <v>0.0042231780420748</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5791966842755003</v>
+        <v>0.5790058038399262</v>
       </c>
       <c r="M7" t="n">
-        <v>0.42860490716063</v>
+        <v>0.4282833874922019</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001550280206497742</v>
+        <v>0.0001728210947310402</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01159403766121748</v>
+        <v>0.01159031009210815</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0196132540297197</v>
+        <v>0.01949340560220514</v>
       </c>
     </row>
     <row r="8">
@@ -847,10 +847,10 @@
         <v>460</v>
       </c>
       <c r="H8" t="n">
-        <v>2.14948589999949</v>
+        <v>1.952973600011319</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02675950000048033</v>
+        <v>0.02004750003106892</v>
       </c>
       <c r="J8" t="n">
         <v>0.003350431699502056</v>
@@ -899,31 +899,31 @@
         <v>751</v>
       </c>
       <c r="H9" t="n">
-        <v>6.085016900000483</v>
+        <v>73.13133320002817</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5870829000014055</v>
+        <v>2.603210599976592</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00549083433393616</v>
+        <v>0.005475805611246416</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003884004951353813</v>
+        <v>0.00388234887383845</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7232667468506284</v>
+        <v>0.7247795426960493</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4043457940781999</v>
+        <v>0.4041642278277143</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.000362574527314616</v>
+        <v>-0.0003724463515099945</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01185433749611986</v>
+        <v>0.01164835102598438</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01995372461417222</v>
+        <v>0.01987024267165116</v>
       </c>
     </row>
     <row r="10">
@@ -951,31 +951,31 @@
         <v>1443</v>
       </c>
       <c r="H10" t="n">
-        <v>10.8923663000005</v>
+        <v>74.11682560003828</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4853268999995635</v>
+        <v>3.197800300025847</v>
       </c>
       <c r="J10" t="n">
-        <v>0.005427129159376408</v>
+        <v>0.005431830420892678</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004190196376467591</v>
+        <v>0.004188381195608319</v>
       </c>
       <c r="L10" t="n">
-        <v>0.595206131803379</v>
+        <v>0.5945045210491231</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4247627244057383</v>
+        <v>0.4245848812866948</v>
       </c>
       <c r="N10" t="n">
-        <v>3.266995589529673e-05</v>
+        <v>4.123289308063305e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01102402512361868</v>
+        <v>0.0110454915088667</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02061842737877606</v>
+        <v>0.02129059973076397</v>
       </c>
     </row>
     <row r="11">
@@ -1003,10 +1003,10 @@
         <v>460</v>
       </c>
       <c r="H11" t="n">
-        <v>2.679104499999085</v>
+        <v>39.58772569999564</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03535109999938868</v>
+        <v>0.06268530001398176</v>
       </c>
       <c r="J11" t="n">
         <v>0.003612363066147454</v>
@@ -1055,31 +1055,31 @@
         <v>752</v>
       </c>
       <c r="H12" t="n">
-        <v>5.810841600001368</v>
+        <v>12.39696580002783</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4871368999993138</v>
+        <v>0.5498910999740474</v>
       </c>
       <c r="J12" t="n">
-        <v>0.005456109402378796</v>
+        <v>0.005466585395023742</v>
       </c>
       <c r="K12" t="n">
-        <v>0.003962737506397006</v>
+        <v>0.003967005923022905</v>
       </c>
       <c r="L12" t="n">
-        <v>0.723232273791699</v>
+        <v>0.7221684387547326</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4127796644064124</v>
+        <v>0.4132411036413509</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0002847813305713081</v>
+        <v>-0.000273687556397415</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01153016214049359</v>
+        <v>0.01150817026694344</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02327963984937664</v>
+        <v>0.02330097132770637</v>
       </c>
     </row>
     <row r="13">
@@ -1107,31 +1107,31 @@
         <v>1442</v>
       </c>
       <c r="H13" t="n">
-        <v>11.42691159999958</v>
+        <v>15.23827539995546</v>
       </c>
       <c r="I13" t="n">
-        <v>0.454641400001492</v>
+        <v>1.347677799989469</v>
       </c>
       <c r="J13" t="n">
-        <v>0.005373914250710142</v>
+        <v>0.005369702339365675</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004111126152188908</v>
+        <v>0.004117275552757502</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6003372324218614</v>
+        <v>0.6009634740733374</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4167303628853549</v>
+        <v>0.4173597111017707</v>
       </c>
       <c r="N13" t="n">
-        <v>4.141692861566695e-05</v>
+        <v>5.309575724253875e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0109990650671753</v>
+        <v>0.01096009745805492</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01859897373055497</v>
+        <v>0.01886274388698117</v>
       </c>
     </row>
     <row r="14">
@@ -1159,10 +1159,10 @@
         <v>460</v>
       </c>
       <c r="H14" t="n">
-        <v>2.799499599999763</v>
+        <v>17.7782048000372</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03451069999937317</v>
+        <v>0.06434889999218285</v>
       </c>
       <c r="J14" t="n">
         <v>0.003448386277010297</v>
@@ -1211,31 +1211,31 @@
         <v>752</v>
       </c>
       <c r="H15" t="n">
-        <v>6.058981399999539</v>
+        <v>47.80041889997665</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5769919000013033</v>
+        <v>1.812901899975259</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00546057977515241</v>
+        <v>0.005458569004796724</v>
       </c>
       <c r="K15" t="n">
-        <v>0.003891003623361923</v>
+        <v>0.003895059294097794</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7290416227651727</v>
+        <v>0.7292411381212847</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4052193439877642</v>
+        <v>0.4056575014023428</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0005112123056083698</v>
+        <v>-0.0004928749061168541</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0119072804909881</v>
+        <v>0.01169580645774585</v>
       </c>
       <c r="P15" t="n">
-        <v>0.02541863189249649</v>
+        <v>0.02517280560104462</v>
       </c>
     </row>
     <row r="16">
@@ -1263,31 +1263,31 @@
         <v>1442</v>
       </c>
       <c r="H16" t="n">
-        <v>9.805827000000136</v>
+        <v>26.1720067000133</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4359764000000723</v>
+        <v>0.5564216000493616</v>
       </c>
       <c r="J16" t="n">
-        <v>0.005224148087803745</v>
+        <v>0.005225496179265574</v>
       </c>
       <c r="K16" t="n">
-        <v>0.003963566642526764</v>
+        <v>0.003965913198451813</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6298961846605465</v>
+        <v>0.6297051494295394</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4017945564919452</v>
+        <v>0.4020256787282329</v>
       </c>
       <c r="N16" t="n">
-        <v>5.960590692603276e-05</v>
+        <v>6.166555364564737e-05</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01062601957519566</v>
+        <v>0.01080921843343031</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01947105096775659</v>
+        <v>0.01961421118665563</v>
       </c>
     </row>
   </sheetData>
